--- a/proposal/collaboration/collaboration_fischer.xlsx
+++ b/proposal/collaboration/collaboration_fischer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10312"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/misunmin/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/misunmin/proj/genesis21b/proposal/collaboration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DF165D-5E1E-3F46-8D9B-32555F755DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF38E030-BBA7-7241-8B1A-C4B0815ACCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5160" yWindow="760" windowWidth="29400" windowHeight="19880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9620" yWindow="5400" windowWidth="29400" windowHeight="19880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="3" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="156">
   <si>
     <r>
       <rPr>
@@ -541,12 +541,21 @@
   <si>
     <t>Wang</t>
   </si>
+  <si>
+    <t>Min, Misun</t>
+  </si>
+  <si>
+    <t>Fischer, Paul</t>
+  </si>
+  <si>
+    <t>fischerp@illinois.edu</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -567,6 +576,14 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1044,10 +1061,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1167,6 +1185,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1180,7 +1201,8 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
@@ -1777,7 +1799,7 @@
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="46" t="s">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="D1" s="46"/>
       <c r="E1" s="3"/>
@@ -1788,7 +1810,7 @@
       </c>
       <c r="B2" s="45"/>
       <c r="C2" s="46" t="s">
-        <v>4</v>
+        <v>153</v>
       </c>
       <c r="D2" s="46"/>
       <c r="E2" s="3"/>
@@ -1799,7 +1821,7 @@
       </c>
       <c r="B3" s="45"/>
       <c r="C3" s="46" t="s">
-        <v>4</v>
+        <v>154</v>
       </c>
       <c r="D3" s="46"/>
       <c r="E3" s="3"/>
@@ -1809,21 +1831,21 @@
         <v>6</v>
       </c>
       <c r="B4" s="45"/>
-      <c r="C4" s="46" t="s">
-        <v>7</v>
+      <c r="C4" s="49" t="s">
+        <v>155</v>
       </c>
       <c r="D4" s="46"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="50"/>
+      <c r="B6" s="51"/>
       <c r="C6" s="47" t="str">
         <f>"Collaborator Table - "&amp;C1&amp;" ("&amp;C2&amp;")"</f>
-        <v>Collaborator Table - Institution Name (Last (Family) Name, First (Given) Name)</v>
+        <v>Collaborator Table - Argonne National Laboratory (Min, Misun)</v>
       </c>
       <c r="D6" s="47"/>
       <c r="E6" s="47"/>
@@ -6486,8 +6508,11 @@
       <formula2>2045</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{06C5BF0F-0C0A-3A44-9E92-4ECFA36AAEA8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
   <headerFooter>
     <oddFooter>&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
@@ -6524,10 +6549,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="45"/>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="52"/>
+      <c r="D1" s="53"/>
       <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -6535,10 +6560,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="45"/>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="52"/>
+      <c r="D2" s="53"/>
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -6546,10 +6571,10 @@
         <v>5</v>
       </c>
       <c r="B3" s="45"/>
-      <c r="C3" s="51" t="s">
+      <c r="C3" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="52"/>
+      <c r="D3" s="53"/>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -6557,18 +6582,18 @@
         <v>6</v>
       </c>
       <c r="B4" s="45"/>
-      <c r="C4" s="51" t="s">
+      <c r="C4" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="52"/>
+      <c r="D4" s="53"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="50"/>
+      <c r="B6" s="51"/>
       <c r="C6" s="47" t="str">
         <f>"Collaborator Table - "&amp;C1&amp;" ("&amp;C2&amp;")"</f>
         <v>Collaborator Table - University of XYZ (Jones, Jane)</v>
@@ -10723,7 +10748,7 @@
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C12:D12 C13:H409 F12:H12">
+  <conditionalFormatting sqref="C12:D12 F12:H12 C13:H409">
     <cfRule type="expression" dxfId="1" priority="3">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>

--- a/proposal/collaboration/collaboration_fischer.xlsx
+++ b/proposal/collaboration/collaboration_fischer.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/misunmin/proj/genesis21b/proposal/collaboration/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fischer1/naomi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF38E030-BBA7-7241-8B1A-C4B0815ACCA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C9239F-F056-8243-BAC3-41C9034643D5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9620" yWindow="5400" windowWidth="29400" windowHeight="19880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3160" yWindow="2960" windowWidth="29400" windowHeight="19880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="3" r:id="rId1"/>
@@ -27,26 +27,17 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Collaborators Example'!$6:$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Senior-Key Personnel'!$6:$7</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="156">
   <si>
     <r>
       <rPr>
@@ -88,22 +79,13 @@
     <t>Lead Applicant Organization:</t>
   </si>
   <si>
-    <t>Institution Name</t>
-  </si>
-  <si>
     <t>Lead Principal Investigator:</t>
   </si>
   <si>
-    <t>Last (Family) Name, First (Given) Name</t>
-  </si>
-  <si>
     <t>Name of person submitting spreadsheet:</t>
   </si>
   <si>
     <t>Email of person submitting spreadsheet:</t>
-  </si>
-  <si>
-    <t>Email address</t>
   </si>
   <si>
     <t>PI or Senior/Key Person</t>
@@ -230,18 +212,9 @@
     <t>advisee</t>
   </si>
   <si>
-    <t>Mirocha</t>
-  </si>
-  <si>
-    <t>Jeffrey</t>
-  </si>
-  <si>
     <t>Lawrence Livermore National Laboratory</t>
   </si>
   <si>
-    <t>0000-0001-5914-6168</t>
-  </si>
-  <si>
     <t>Pacific Northwest National Laboratory</t>
   </si>
   <si>
@@ -314,12 +287,6 @@
     <t>Barcelona Supercomputing Center</t>
   </si>
   <si>
-    <t>Rowe</t>
-  </si>
-  <si>
-    <t>Kris</t>
-  </si>
-  <si>
     <t>Warburton</t>
   </si>
   <si>
@@ -344,57 +311,18 @@
     <t>Derek</t>
   </si>
   <si>
-    <t>Yuan</t>
-  </si>
-  <si>
-    <t>Haomin</t>
-  </si>
-  <si>
     <t>Shaver</t>
   </si>
   <si>
     <t>Dillon</t>
   </si>
   <si>
-    <t>Obabko</t>
-  </si>
-  <si>
-    <t>Balakrishnan</t>
-  </si>
-  <si>
-    <t>Ramesh</t>
-  </si>
-  <si>
-    <t>Siegel</t>
-  </si>
-  <si>
-    <t>Andrew</t>
-  </si>
-  <si>
-    <t>Jun</t>
-  </si>
-  <si>
-    <t>Feng</t>
-  </si>
-  <si>
-    <t>Kotamarthi</t>
-  </si>
-  <si>
-    <t>Rao</t>
-  </si>
-  <si>
     <t>Argonne National Laboratory</t>
   </si>
   <si>
     <t>Idaho National Laboratory</t>
   </si>
   <si>
-    <t>Patel</t>
-  </si>
-  <si>
-    <t>Saumil</t>
-  </si>
-  <si>
     <t>Karakus</t>
   </si>
   <si>
@@ -464,24 +392,9 @@
     <t>University of Ulsan, Korea</t>
   </si>
   <si>
-    <t>Novak</t>
-  </si>
-  <si>
-    <t>April</t>
-  </si>
-  <si>
     <t>Yonsei University, Korea</t>
   </si>
   <si>
-    <t>Aleksandr</t>
-  </si>
-  <si>
-    <t>Kerkemeier</t>
-  </si>
-  <si>
-    <t>Stefan</t>
-  </si>
-  <si>
     <t>Hassan</t>
   </si>
   <si>
@@ -491,12 +404,6 @@
     <t>Texas A&amp;M University</t>
   </si>
   <si>
-    <t xml:space="preserve">Fytanidis </t>
-  </si>
-  <si>
-    <t>Dmitrios</t>
-  </si>
-  <si>
     <t>Frouzakis</t>
   </si>
   <si>
@@ -549,6 +456,90 @@
   </si>
   <si>
     <t>fischerp@illinois.edu</t>
+  </si>
+  <si>
+    <t>University of Illinois Urbana Champaign / Argonne National Laboratory</t>
+  </si>
+  <si>
+    <t>Olson</t>
+  </si>
+  <si>
+    <t>Luke</t>
+  </si>
+  <si>
+    <t>University of Illinois Urbana Champaign</t>
+  </si>
+  <si>
+    <t>Pennsylvania State University</t>
+  </si>
+  <si>
+    <t>Vinuesa</t>
+  </si>
+  <si>
+    <t>Ricardo</t>
+  </si>
+  <si>
+    <t>University of Michigan</t>
+  </si>
+  <si>
+    <t>Leyffer</t>
+  </si>
+  <si>
+    <t>Sven</t>
+  </si>
+  <si>
+    <t>Andrej</t>
+  </si>
+  <si>
+    <t>Julian</t>
+  </si>
+  <si>
+    <t>Tsai</t>
+  </si>
+  <si>
+    <t>Ping-Hsuan</t>
+  </si>
+  <si>
+    <t>Philipps</t>
+  </si>
+  <si>
+    <t>Malachi</t>
+  </si>
+  <si>
+    <t>Sandia National Laboratory</t>
+  </si>
+  <si>
+    <t>Kaneko</t>
+  </si>
+  <si>
+    <t>Kento</t>
+  </si>
+  <si>
+    <t>Massachussets Institute of Technology</t>
+  </si>
+  <si>
+    <t>Patera</t>
+  </si>
+  <si>
+    <t>Anthony</t>
+  </si>
+  <si>
+    <t>Karniadakis</t>
+  </si>
+  <si>
+    <t>George</t>
+  </si>
+  <si>
+    <t>Brown University</t>
+  </si>
+  <si>
+    <t>Balachandar</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>University of Florida</t>
   </si>
 </sst>
 </file>
@@ -1179,6 +1170,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1187,12 +1184,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1570,44 +1561,44 @@
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="46" t="s">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="D1" s="46"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="45" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="45"/>
       <c r="C2" s="46" t="s">
-        <v>4</v>
+        <v>125</v>
       </c>
       <c r="D2" s="46"/>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="45" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B3" s="45"/>
       <c r="C3" s="46" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="D3" s="46"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="45" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" s="45"/>
-      <c r="C4" s="46" t="s">
-        <v>7</v>
+      <c r="C4" s="51" t="s">
+        <v>127</v>
       </c>
       <c r="D4" s="46"/>
     </row>
     <row r="5" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="43" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" s="44"/>
       <c r="C6" s="39"/>
@@ -1615,79 +1606,125 @@
     </row>
     <row r="7" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="37" t="s">
         <v>9</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="29" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="31" t="s">
         <v>52</v>
       </c>
+      <c r="C8" s="31"/>
       <c r="D8" s="32" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="33"/>
-      <c r="B9" s="26"/>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A9" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>54</v>
+      </c>
       <c r="C9" s="27"/>
-      <c r="D9" s="34"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="33"/>
-      <c r="B10" s="26"/>
+      <c r="D9" s="34" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>130</v>
+      </c>
       <c r="C10" s="27"/>
-      <c r="D10" s="34"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="33"/>
-      <c r="B11" s="26"/>
+      <c r="D10" s="34" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>56</v>
+      </c>
       <c r="C11" s="27"/>
-      <c r="D11" s="34"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="33"/>
-      <c r="B12" s="26"/>
+      <c r="D11" s="34" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>80</v>
+      </c>
       <c r="C12" s="27"/>
-      <c r="D12" s="34"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="33"/>
-      <c r="B13" s="26"/>
+      <c r="D12" s="34" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>57</v>
+      </c>
       <c r="C13" s="27"/>
-      <c r="D13" s="34"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="33"/>
-      <c r="B14" s="26"/>
+      <c r="D13" s="34" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="33" t="s">
+        <v>133</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>134</v>
+      </c>
       <c r="C14" s="27"/>
-      <c r="D14" s="34"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="33"/>
-      <c r="B15" s="26"/>
+      <c r="D14" s="34" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>137</v>
+      </c>
       <c r="C15" s="27"/>
-      <c r="D15" s="34"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="33"/>
-      <c r="B16" s="26"/>
+      <c r="D15" s="34" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>139</v>
+      </c>
       <c r="C16" s="27"/>
-      <c r="D16" s="34"/>
+      <c r="D16" s="34" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="33"/>
@@ -1772,8 +1809,11 @@
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{6615D0BB-E1DA-9047-8ABF-D0F2CEE80405}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
   <headerFooter>
     <oddFooter>&amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
@@ -1782,7 +1822,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H411"/>
+  <dimension ref="A1:H398"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="22.6640625" customWidth="1"/>
@@ -1799,153 +1839,153 @@
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="46" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D1" s="46"/>
       <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="45" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="45"/>
       <c r="C2" s="46" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="D2" s="46"/>
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="45" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B3" s="45"/>
       <c r="C3" s="46" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="D3" s="46"/>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="45" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" s="45"/>
-      <c r="C4" s="49" t="s">
-        <v>155</v>
+      <c r="C4" s="51" t="s">
+        <v>127</v>
       </c>
       <c r="D4" s="46"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="50" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="47" t="str">
+      <c r="A6" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="48"/>
+      <c r="C6" s="49" t="str">
         <f>"Collaborator Table - "&amp;C1&amp;" ("&amp;C2&amp;")"</f>
         <v>Collaborator Table - Argonne National Laboratory (Min, Misun)</v>
       </c>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="48"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
     </row>
     <row r="7" spans="1:8" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="G7" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="23" t="s">
+      <c r="H7" s="24" t="s">
         <v>11</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="24" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="17" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H8" s="19">
         <v>2023</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>131</v>
+        <v>62</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="E9" s="17"/>
       <c r="F9" s="17" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H9" s="19">
         <v>2023</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E10" s="17"/>
       <c r="F10" s="17" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H10" s="19">
         <v>2023</v>
@@ -1953,215 +1993,215 @@
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E11" s="17"/>
       <c r="F11" s="17" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H11" s="19">
         <v>2023</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E12" s="17"/>
       <c r="F12" s="17" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H12" s="19">
         <v>2023</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="19">
-        <v>2023</v>
+        <v>116</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="7">
+        <v>2020</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="H14" s="19">
+        <v>54</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="7">
         <v>2023</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="B15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="D15" s="41" t="s">
-        <v>146</v>
+      <c r="D15" s="42" t="s">
+        <v>34</v>
       </c>
       <c r="E15" s="41"/>
       <c r="F15" s="41" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G15" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="7">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="7">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="D16" s="41" t="s">
-        <v>37</v>
+      <c r="D16" s="42" t="s">
+        <v>119</v>
       </c>
       <c r="E16" s="41"/>
       <c r="F16" s="41" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H16" s="7">
         <v>2023</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="42" t="s">
-        <v>37</v>
+        <v>68</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>69</v>
       </c>
       <c r="E17" s="41"/>
       <c r="F17" s="41" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H17" s="7">
         <v>2023</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="42" t="s">
-        <v>147</v>
+        <v>71</v>
+      </c>
+      <c r="D18" s="41" t="s">
+        <v>72</v>
       </c>
       <c r="E18" s="41"/>
       <c r="F18" s="41" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H18" s="7">
         <v>2023</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C19" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="41" t="s">
         <v>74</v>
-      </c>
-      <c r="D19" s="41" t="s">
-        <v>75</v>
       </c>
       <c r="E19" s="41"/>
       <c r="F19" s="41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H19" s="7">
         <v>2023</v>
@@ -2169,23 +2209,23 @@
     </row>
     <row r="20" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D20" s="41" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E20" s="41"/>
       <c r="F20" s="41" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="H20" s="7">
         <v>2023</v>
@@ -2193,143 +2233,143 @@
     </row>
     <row r="21" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E21" s="41"/>
       <c r="F21" s="41" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="H21" s="7">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D22" s="41" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E22" s="41"/>
       <c r="F22" s="41" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="H22" s="7">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C23" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="41" t="s">
         <v>89</v>
-      </c>
-      <c r="D23" s="41" t="s">
-        <v>90</v>
       </c>
       <c r="E23" s="41"/>
       <c r="F23" s="41" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="H23" s="7">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C24" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="41" t="s">
         <v>91</v>
-      </c>
-      <c r="D24" s="41" t="s">
-        <v>130</v>
       </c>
       <c r="E24" s="41"/>
       <c r="F24" s="41" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="H24" s="7">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="D25" s="41" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="E25" s="41"/>
       <c r="F25" s="41" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="H25" s="7">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="D26" s="41" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E26" s="41"/>
       <c r="F26" s="41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H26" s="7">
         <v>2023</v>
@@ -2337,47 +2377,47 @@
     </row>
     <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D27" s="41" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E27" s="41"/>
       <c r="F27" s="41" t="s">
         <v>100</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="H27" s="7">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D28" s="41" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E28" s="41"/>
       <c r="F28" s="41" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="H28" s="7">
         <v>2023</v>
@@ -2385,23 +2425,23 @@
     </row>
     <row r="29" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D29" s="41" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E29" s="41"/>
       <c r="F29" s="41" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="H29" s="7">
         <v>2023</v>
@@ -2409,71 +2449,71 @@
     </row>
     <row r="30" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="D30" s="41" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="E30" s="41"/>
       <c r="F30" s="41" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H30" s="7">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D31" s="41" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E31" s="41"/>
       <c r="F31" s="41" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H31" s="7">
-        <v>2018</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="D32" s="41" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="E32" s="41"/>
       <c r="F32" s="41" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="H32" s="7">
         <v>2023</v>
@@ -2481,363 +2521,265 @@
     </row>
     <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="E33" s="41"/>
       <c r="F33" s="41" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="H33" s="7">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="E34" s="41"/>
       <c r="F34" s="41" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="H34" s="7">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C35" s="42" t="s">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="D35" s="41" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="E35" s="41"/>
       <c r="F35" s="41" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H35" s="7">
-        <v>2022</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C36" s="42" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="D36" s="41" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
       <c r="E36" s="41"/>
       <c r="F36" s="41" t="s">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H36" s="7">
-        <v>2022</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B37" s="15" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C37" s="42" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="D37" s="41" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="E37" s="41"/>
       <c r="F37" s="41" t="s">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H37" s="7">
-        <v>2020</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C38" s="42" t="s">
-        <v>43</v>
+        <v>148</v>
       </c>
       <c r="D38" s="41" t="s">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="E38" s="41"/>
       <c r="F38" s="41" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="H38" s="7">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C39" s="42" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="D39" s="41" t="s">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="E39" s="41"/>
       <c r="F39" s="41" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H39" s="7">
-        <v>2020</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="C40" s="42" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="D40" s="41" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="E40" s="41"/>
       <c r="F40" s="41" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H40" s="7">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C41" s="42" t="s">
-        <v>124</v>
-      </c>
-      <c r="D41" s="41" t="s">
-        <v>125</v>
-      </c>
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="14"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="41"/>
       <c r="E41" s="41"/>
-      <c r="F41" s="41" t="s">
-        <v>129</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H41" s="7">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="42" t="s">
-        <v>133</v>
-      </c>
-      <c r="D42" s="41" t="s">
-        <v>134</v>
-      </c>
+      <c r="F41" s="41"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="7"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" s="14"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="41"/>
       <c r="E42" s="41"/>
-      <c r="F42" s="41" t="s">
-        <v>135</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H42" s="7">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C43" s="42" t="s">
-        <v>136</v>
-      </c>
-      <c r="D43" s="41" t="s">
-        <v>137</v>
-      </c>
+      <c r="F42" s="41"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="7"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" s="14"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="42"/>
+      <c r="D43" s="41"/>
       <c r="E43" s="41"/>
-      <c r="F43" s="41" t="s">
-        <v>100</v>
-      </c>
-      <c r="G43" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H43" s="7">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C44" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="D44" s="41" t="s">
-        <v>139</v>
-      </c>
+      <c r="F43" s="41"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="7"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="14"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="42"/>
+      <c r="D44" s="41"/>
       <c r="E44" s="41"/>
-      <c r="F44" s="41" t="s">
-        <v>140</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H44" s="7">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C45" s="42" t="s">
-        <v>141</v>
-      </c>
-      <c r="D45" s="41" t="s">
-        <v>142</v>
-      </c>
+      <c r="F44" s="41"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="7"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="14"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="41"/>
       <c r="E45" s="41"/>
-      <c r="F45" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="G45" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H45" s="7">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A46" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C46" s="42" t="s">
-        <v>148</v>
-      </c>
-      <c r="D46" s="41" t="s">
-        <v>149</v>
-      </c>
+      <c r="F45" s="41"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="7"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="14"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="42"/>
+      <c r="D46" s="41"/>
       <c r="E46" s="41"/>
-      <c r="F46" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H46" s="7">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C47" s="42" t="s">
-        <v>152</v>
-      </c>
-      <c r="D47" s="41" t="s">
-        <v>151</v>
-      </c>
+      <c r="F46" s="41"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="7"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" s="14"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="42"/>
+      <c r="D47" s="41"/>
       <c r="E47" s="41"/>
-      <c r="F47" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H47" s="7">
-        <v>2023</v>
-      </c>
+      <c r="F47" s="41"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="7"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="14"/>
@@ -3420,7 +3362,7 @@
       <c r="H105" s="7"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A106" s="14"/>
+      <c r="A106" s="4"/>
       <c r="B106" s="5"/>
       <c r="C106" s="42"/>
       <c r="D106" s="41"/>
@@ -3430,7 +3372,7 @@
       <c r="H106" s="7"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A107" s="14"/>
+      <c r="A107" s="4"/>
       <c r="B107" s="5"/>
       <c r="C107" s="42"/>
       <c r="D107" s="41"/>
@@ -3440,7 +3382,7 @@
       <c r="H107" s="7"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A108" s="14"/>
+      <c r="A108" s="4"/>
       <c r="B108" s="5"/>
       <c r="C108" s="42"/>
       <c r="D108" s="41"/>
@@ -3450,7 +3392,7 @@
       <c r="H108" s="7"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A109" s="14"/>
+      <c r="A109" s="4"/>
       <c r="B109" s="5"/>
       <c r="C109" s="42"/>
       <c r="D109" s="41"/>
@@ -3460,7 +3402,7 @@
       <c r="H109" s="7"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A110" s="14"/>
+      <c r="A110" s="4"/>
       <c r="B110" s="5"/>
       <c r="C110" s="42"/>
       <c r="D110" s="41"/>
@@ -3470,7 +3412,7 @@
       <c r="H110" s="7"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A111" s="14"/>
+      <c r="A111" s="4"/>
       <c r="B111" s="5"/>
       <c r="C111" s="42"/>
       <c r="D111" s="41"/>
@@ -3480,7 +3422,7 @@
       <c r="H111" s="7"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A112" s="14"/>
+      <c r="A112" s="4"/>
       <c r="B112" s="5"/>
       <c r="C112" s="42"/>
       <c r="D112" s="41"/>
@@ -3490,7 +3432,7 @@
       <c r="H112" s="7"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A113" s="14"/>
+      <c r="A113" s="4"/>
       <c r="B113" s="5"/>
       <c r="C113" s="42"/>
       <c r="D113" s="41"/>
@@ -3500,7 +3442,7 @@
       <c r="H113" s="7"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A114" s="14"/>
+      <c r="A114" s="4"/>
       <c r="B114" s="5"/>
       <c r="C114" s="42"/>
       <c r="D114" s="41"/>
@@ -3510,7 +3452,7 @@
       <c r="H114" s="7"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A115" s="14"/>
+      <c r="A115" s="4"/>
       <c r="B115" s="5"/>
       <c r="C115" s="42"/>
       <c r="D115" s="41"/>
@@ -3520,7 +3462,7 @@
       <c r="H115" s="7"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A116" s="14"/>
+      <c r="A116" s="4"/>
       <c r="B116" s="5"/>
       <c r="C116" s="42"/>
       <c r="D116" s="41"/>
@@ -3530,7 +3472,7 @@
       <c r="H116" s="7"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A117" s="14"/>
+      <c r="A117" s="4"/>
       <c r="B117" s="5"/>
       <c r="C117" s="42"/>
       <c r="D117" s="41"/>
@@ -3540,7 +3482,7 @@
       <c r="H117" s="7"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A118" s="14"/>
+      <c r="A118" s="4"/>
       <c r="B118" s="5"/>
       <c r="C118" s="42"/>
       <c r="D118" s="41"/>
@@ -6339,171 +6281,41 @@
       <c r="G397" s="6"/>
       <c r="H397" s="7"/>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A398" s="4"/>
-      <c r="B398" s="5"/>
-      <c r="C398" s="42"/>
-      <c r="D398" s="41"/>
-      <c r="E398" s="41"/>
-      <c r="F398" s="41"/>
-      <c r="G398" s="6"/>
-      <c r="H398" s="7"/>
-    </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A399" s="4"/>
-      <c r="B399" s="5"/>
-      <c r="C399" s="42"/>
-      <c r="D399" s="41"/>
-      <c r="E399" s="41"/>
-      <c r="F399" s="41"/>
-      <c r="G399" s="6"/>
-      <c r="H399" s="7"/>
-    </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A400" s="4"/>
-      <c r="B400" s="5"/>
-      <c r="C400" s="42"/>
-      <c r="D400" s="41"/>
-      <c r="E400" s="41"/>
-      <c r="F400" s="41"/>
-      <c r="G400" s="6"/>
-      <c r="H400" s="7"/>
-    </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A401" s="4"/>
-      <c r="B401" s="5"/>
-      <c r="C401" s="42"/>
-      <c r="D401" s="41"/>
-      <c r="E401" s="41"/>
-      <c r="F401" s="41"/>
-      <c r="G401" s="6"/>
-      <c r="H401" s="7"/>
-    </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A402" s="4"/>
-      <c r="B402" s="5"/>
-      <c r="C402" s="42"/>
-      <c r="D402" s="41"/>
-      <c r="E402" s="41"/>
-      <c r="F402" s="41"/>
-      <c r="G402" s="6"/>
-      <c r="H402" s="7"/>
-    </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A403" s="4"/>
-      <c r="B403" s="5"/>
-      <c r="C403" s="42"/>
-      <c r="D403" s="41"/>
-      <c r="E403" s="41"/>
-      <c r="F403" s="41"/>
-      <c r="G403" s="6"/>
-      <c r="H403" s="7"/>
-    </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A404" s="4"/>
-      <c r="B404" s="5"/>
-      <c r="C404" s="42"/>
-      <c r="D404" s="41"/>
-      <c r="E404" s="41"/>
-      <c r="F404" s="41"/>
-      <c r="G404" s="6"/>
-      <c r="H404" s="7"/>
-    </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A405" s="4"/>
-      <c r="B405" s="5"/>
-      <c r="C405" s="42"/>
-      <c r="D405" s="41"/>
-      <c r="E405" s="41"/>
-      <c r="F405" s="41"/>
-      <c r="G405" s="6"/>
-      <c r="H405" s="7"/>
-    </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A406" s="4"/>
-      <c r="B406" s="5"/>
-      <c r="C406" s="42"/>
-      <c r="D406" s="41"/>
-      <c r="E406" s="41"/>
-      <c r="F406" s="41"/>
-      <c r="G406" s="6"/>
-      <c r="H406" s="7"/>
-    </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A407" s="4"/>
-      <c r="B407" s="5"/>
-      <c r="C407" s="42"/>
-      <c r="D407" s="41"/>
-      <c r="E407" s="41"/>
-      <c r="F407" s="41"/>
-      <c r="G407" s="6"/>
-      <c r="H407" s="7"/>
-    </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A408" s="4"/>
-      <c r="B408" s="5"/>
-      <c r="C408" s="42"/>
-      <c r="D408" s="41"/>
-      <c r="E408" s="41"/>
-      <c r="F408" s="41"/>
-      <c r="G408" s="6"/>
-      <c r="H408" s="7"/>
-    </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A409" s="4"/>
-      <c r="B409" s="5"/>
-      <c r="C409" s="42"/>
-      <c r="D409" s="41"/>
-      <c r="E409" s="41"/>
-      <c r="F409" s="41"/>
-      <c r="G409" s="6"/>
-      <c r="H409" s="7"/>
-    </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A410" s="4"/>
-      <c r="B410" s="5"/>
-      <c r="C410" s="42"/>
-      <c r="D410" s="41"/>
-      <c r="E410" s="41"/>
-      <c r="F410" s="41"/>
-      <c r="G410" s="6"/>
-      <c r="H410" s="7"/>
-    </row>
-    <row r="411" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A411" s="8"/>
-      <c r="B411" s="9"/>
-      <c r="C411" s="10"/>
-      <c r="D411" s="11"/>
-      <c r="E411" s="11"/>
-      <c r="F411" s="11"/>
-      <c r="G411" s="12"/>
-      <c r="H411" s="13"/>
+    <row r="398" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A398" s="8"/>
+      <c r="B398" s="9"/>
+      <c r="C398" s="10"/>
+      <c r="D398" s="11"/>
+      <c r="E398" s="11"/>
+      <c r="F398" s="11"/>
+      <c r="G398" s="12"/>
+      <c r="H398" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:B411">
+  <conditionalFormatting sqref="A8:B398">
     <cfRule type="expression" dxfId="4" priority="2">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C8:H411">
+  <conditionalFormatting sqref="C8:H398">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8:H411" xr:uid="{A3DF8C03-8B15-444D-AE35-1A6E2A7E55AE}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8:H398" xr:uid="{A3DF8C03-8B15-444D-AE35-1A6E2A7E55AE}">
       <formula1>1945</formula1>
       <formula2>2045</formula2>
     </dataValidation>
@@ -6523,7 +6335,7 @@
           <x14:formula1>
             <xm:f>LOV!$A$1:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>G18:G44 G46:G411 G8:G16</xm:sqref>
+          <xm:sqref>G33:G398 G8:G14 G16:G31</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6550,107 +6362,107 @@
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="52" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="45" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="45"/>
       <c r="C2" s="52" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D2" s="53"/>
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="45" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B3" s="45"/>
       <c r="C3" s="52" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D3" s="53"/>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="45" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" s="45"/>
       <c r="C4" s="52" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D4" s="53"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="50" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="47" t="str">
+      <c r="A6" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="48"/>
+      <c r="C6" s="49" t="str">
         <f>"Collaborator Table - "&amp;C1&amp;" ("&amp;C2&amp;")"</f>
         <v>Collaborator Table - University of XYZ (Jones, Jane)</v>
       </c>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="48"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="50"/>
     </row>
     <row r="7" spans="1:8" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="G7" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="23" t="s">
+      <c r="H7" s="24" t="s">
         <v>11</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="24" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="E8" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="F8" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="41" t="s">
+      <c r="G8" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="E8" s="41" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="H8" s="7">
         <v>2021</v>
@@ -6658,25 +6470,25 @@
     </row>
     <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C9" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="G9" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="E9" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="H9" s="7">
         <v>2019</v>
@@ -6684,25 +6496,25 @@
     </row>
     <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C10" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="41" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="G10" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="E10" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>35</v>
       </c>
       <c r="H10" s="7">
         <v>2020</v>
@@ -6710,25 +6522,25 @@
     </row>
     <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="E11" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="F11" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="G11" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="E11" s="41" t="s">
-        <v>40</v>
-      </c>
-      <c r="F11" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="H11" s="7">
         <v>2017</v>
@@ -6736,25 +6548,25 @@
     </row>
     <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C12" s="42" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="41" t="s">
+      <c r="G12" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>47</v>
       </c>
       <c r="H12" s="7">
         <v>2021</v>
@@ -10794,32 +10606,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -10829,6 +10641,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001733C14AC8EC6F498F123411DB8BC020" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c1f196d61ef494b6c4f62f58be5bb14e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7b7cc8fe-90e2-43f3-ad3c-00f457ec8258" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="46c76a5a58717c3453de3c52cd271f55" ns2:_="">
     <xsd:import namespace="7b7cc8fe-90e2-43f3-ad3c-00f457ec8258"/>
@@ -10960,22 +10787,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ACA6411-41A0-4B6C-874D-1FC05CC4B568}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53ACD002-FFBE-4185-9DDB-0AA3A824C3C1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE70D9AC-1270-4AD5-BB63-23D2B0A32B51}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10991,21 +10820,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53ACD002-FFBE-4185-9DDB-0AA3A824C3C1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ACA6411-41A0-4B6C-874D-1FC05CC4B568}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>